--- a/test_data/mercury_e1.xlsx
+++ b/test_data/mercury_e1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="18" activeTab="23"/>
+    <workbookView windowWidth="25600" windowHeight="11870" firstSheet="19" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -255,19 +255,19 @@
     <t>腕关节奇异发送坐标报错</t>
   </si>
   <si>
-    <t>[0,0,-90,0,90,0]</t>
+    <t>[0,0,0,-90,0,0,0]</t>
   </si>
   <si>
     <t>肩关节奇异发送坐标报错</t>
   </si>
   <si>
-    <t>[-11.82, 36.78, -101.57, 70.74, 8.98, 0.0]</t>
+    <t>[0,-30,0,-70,0,0,0]</t>
   </si>
   <si>
     <t>肘关节奇异发送坐标报错</t>
   </si>
   <si>
-    <t>[-8.75, -44.21, -7.2, 48.05, 8.98, 0.0]</t>
+    <t>[0,50,0,0,0,50,0]</t>
   </si>
   <si>
     <t>奇异点报错清除错误信息</t>
@@ -930,19 +930,19 @@
     <t>is_in_position</t>
   </si>
   <si>
+    <t>[0, -10, 0, -90, 0, -90, 0]</t>
+  </si>
+  <si>
+    <t>[1.1, -10, 0, -90, 0, -90, 0]</t>
+  </si>
+  <si>
+    <t>是否到达指定点位（坐标）</t>
+  </si>
+  <si>
+    <t>[210.5, -0.1, 418.1, -179.99, 9.99, 179.96]</t>
+  </si>
+  <si>
     <t>[0, 30, -100, -20, 0.0, 0.0]</t>
-  </si>
-  <si>
-    <t>[1.1, 30, -100, -20, 0.0, 0.0]</t>
-  </si>
-  <si>
-    <t>是否到达指定点位（坐标）</t>
-  </si>
-  <si>
-    <t>[169.5, -85.4, 365.2, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[169.5, -88.4, 365.2, 179.99, 0.0, -90.0]</t>
   </si>
   <si>
     <t>[149.9, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
@@ -3055,7 +3055,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -3080,7 +3080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3109,17 +3109,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3169,18 +3169,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="42.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.3363636363636" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:8">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:8">
+    <row r="5" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3285,14 +3285,14 @@
       <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G5" s="1">
         <v>36</v>
@@ -3311,18 +3311,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3401,18 +3401,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3462,17 +3462,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3658,17 +3658,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="18.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.2545454545455" style="4" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3854,18 +3854,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3915,18 +3915,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3976,18 +3976,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4051,15 +4051,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1111111111111" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1090909090909" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4135,7 +4135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:8">
+    <row r="4" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:8">
+    <row r="5" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="43.2" spans="1:8">
+    <row r="6" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="43.2" spans="1:8">
+    <row r="7" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="43.2" spans="1:8">
+    <row r="8" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="43.2" spans="1:8">
+    <row r="9" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:8">
+    <row r="10" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:8">
+    <row r="11" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:8">
+    <row r="13" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:8">
+    <row r="14" ht="42" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="43.2" spans="1:8">
+    <row r="15" ht="42" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="43.2" spans="1:8">
+    <row r="16" ht="42" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" ht="43.2" spans="1:8">
+    <row r="17" ht="42" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" ht="43.2" spans="1:8">
+    <row r="18" ht="42" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:8">
+    <row r="19" ht="42" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:8">
+    <row r="20" ht="42" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" ht="43.2" spans="1:8">
+    <row r="21" ht="42" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="43.2" spans="1:8">
+    <row r="22" ht="42" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" ht="43.2" spans="1:8">
+    <row r="23" ht="42" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" ht="43.2" spans="1:8">
+    <row r="24" ht="42" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" ht="43.2" spans="1:8">
+    <row r="25" ht="42" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" ht="43.2" spans="1:8">
+    <row r="26" ht="42" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" ht="43.2" spans="1:8">
+    <row r="27" ht="42" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" ht="43.2" spans="1:8">
+    <row r="28" ht="42" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" ht="43.2" spans="1:8">
+    <row r="29" ht="42" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" ht="43.2" spans="1:8">
+    <row r="30" ht="42" spans="1:8">
       <c r="A30" s="2">
         <v>15</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" ht="43.2" spans="1:8">
+    <row r="31" ht="42" spans="1:8">
       <c r="A31" s="2">
         <v>16</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" ht="43.2" spans="1:8">
+    <row r="32" ht="42" spans="1:8">
       <c r="A32" s="2">
         <v>17</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" ht="43.2" spans="1:8">
+    <row r="33" ht="42" spans="1:8">
       <c r="A33" s="2">
         <v>18</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" ht="43.2" spans="1:8">
+    <row r="34" ht="42" spans="1:8">
       <c r="A34" s="2">
         <v>19</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" ht="43.2" spans="1:8">
+    <row r="35" ht="42" spans="1:8">
       <c r="A35" s="2">
         <v>20</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" ht="43.2" spans="1:8">
+    <row r="36" ht="42" spans="1:8">
       <c r="A36" s="2">
         <v>21</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" ht="43.2" spans="1:8">
+    <row r="37" ht="42" spans="1:8">
       <c r="A37" s="2">
         <v>22</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" ht="43.2" spans="1:8">
+    <row r="38" ht="42" spans="1:8">
       <c r="A38" s="2">
         <v>23</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" ht="43.2" spans="1:8">
+    <row r="39" ht="42" spans="1:8">
       <c r="A39" s="2">
         <v>24</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" ht="43.2" spans="1:8">
+    <row r="40" ht="42" spans="1:8">
       <c r="A40" s="2">
         <v>25</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" ht="43.2" spans="1:8">
+    <row r="41" ht="42" spans="1:8">
       <c r="A41" s="2">
         <v>26</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" ht="43.2" spans="1:8">
+    <row r="42" ht="42" spans="1:8">
       <c r="A42" s="2">
         <v>27</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" ht="43.2" spans="1:8">
+    <row r="43" ht="42" spans="1:8">
       <c r="A43" s="2">
         <v>28</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" ht="28.8" spans="1:8">
+    <row r="44" ht="28" spans="1:8">
       <c r="A44" s="2">
         <v>29</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" ht="28.8" spans="1:8">
+    <row r="45" ht="28" spans="1:8">
       <c r="A45" s="2">
         <v>30</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" ht="28.8" spans="1:8">
+    <row r="46" ht="28" spans="1:8">
       <c r="A46" s="2">
         <v>31</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" ht="28.8" spans="1:8">
+    <row r="47" ht="28" spans="1:8">
       <c r="A47" s="2">
         <v>32</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" ht="28.8" spans="1:8">
+    <row r="48" ht="28" spans="1:8">
       <c r="A48" s="2">
         <v>33</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" ht="28.8" spans="1:8">
+    <row r="49" ht="28" spans="1:8">
       <c r="A49" s="2">
         <v>34</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" ht="28.8" spans="1:8">
+    <row r="50" ht="28" spans="1:8">
       <c r="A50" s="2">
         <v>35</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" ht="28.8" spans="1:8">
+    <row r="51" ht="28" spans="1:8">
       <c r="A51" s="2">
         <v>36</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" ht="28.8" spans="1:8">
+    <row r="52" ht="28" spans="1:8">
       <c r="A52" s="2">
         <v>37</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" ht="28.8" spans="1:8">
+    <row r="53" ht="28" spans="1:8">
       <c r="A53" s="2">
         <v>38</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" ht="28.8" spans="1:8">
+    <row r="54" ht="28" spans="1:8">
       <c r="A54" s="2">
         <v>39</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" ht="28.8" spans="1:8">
+    <row r="55" ht="28" spans="1:8">
       <c r="A55" s="2">
         <v>40</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" ht="28.8" spans="1:8">
+    <row r="56" ht="28" spans="1:8">
       <c r="A56" s="2">
         <v>41</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" ht="28.8" spans="1:8">
+    <row r="57" ht="28" spans="1:8">
       <c r="A57" s="2">
         <v>42</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" ht="28.8" spans="1:8">
+    <row r="58" ht="28" spans="1:8">
       <c r="A58" s="2">
         <v>43</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" ht="28.8" spans="1:8">
+    <row r="59" ht="28" spans="1:8">
       <c r="A59" s="2">
         <v>44</v>
       </c>
@@ -5469,7 +5469,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -5494,7 +5494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5523,14 +5523,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5694,7 +5694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:6">
+    <row r="9" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:6">
+    <row r="10" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -5738,18 +5738,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1111111111111" style="1" customWidth="1"/>
-    <col min="7" max="9" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1090909090909" style="1" customWidth="1"/>
+    <col min="7" max="9" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="22" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="23" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="24" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="26" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="27" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="29" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="30" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A30" s="2">
         <v>15</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="31" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A31" s="2">
         <v>16</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="32" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A32" s="2">
         <v>17</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="33" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A33" s="2">
         <v>18</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="34" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A34" s="2">
         <v>19</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="35" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A35" s="2">
         <v>20</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="36" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A36" s="2">
         <v>21</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="37" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A37" s="2">
         <v>22</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="38" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A38" s="2">
         <v>23</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="39" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A39" s="2">
         <v>24</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="40" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A40" s="2">
         <v>25</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="41" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A41" s="2">
         <v>26</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="42" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A42" s="2">
         <v>27</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="43" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A43" s="2">
         <v>28</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="44" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A44" s="2">
         <v>29</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="45" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A45" s="2">
         <v>30</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="46" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A46" s="2">
         <v>31</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="47" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A47" s="2">
         <v>32</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="48" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A48" s="2">
         <v>33</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="49" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A49" s="2">
         <v>34</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="50" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A50" s="2">
         <v>35</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="51" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A51" s="2">
         <v>36</v>
       </c>
@@ -7138,7 +7138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="52" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A52" s="2">
         <v>37</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="53" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A53" s="2">
         <v>38</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="54" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A54" s="2">
         <v>39</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="55" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A55" s="2">
         <v>40</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="56" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A56" s="2">
         <v>41</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="57" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A57" s="2">
         <v>42</v>
       </c>
@@ -7332,14 +7332,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.3796296296296" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.3818181818182" style="1" customWidth="1"/>
     <col min="5" max="5" width="50" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7465,7 +7465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:6">
+    <row r="8" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7495,18 +7495,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
     <col min="2" max="2" width="28" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -7802,13 +7802,13 @@
         <v>60</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A26" s="2">
         <v>13</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A27" s="2">
         <v>14</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A28" s="2">
         <v>15</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A29" s="2">
         <v>16</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A30" s="2">
         <v>17</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A31" s="2">
         <v>18</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="32" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A32" s="2">
         <v>19</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="33" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A33" s="2">
         <v>20</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="34" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A34" s="2">
         <v>21</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="35" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A35" s="2">
         <v>22</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="36" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A36" s="2">
         <v>23</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="37" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A37" s="2">
         <v>24</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="38" s="1" customFormat="1" spans="1:8">
       <c r="A38" s="2">
         <v>25</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="39" s="1" customFormat="1" spans="1:8">
       <c r="A39" s="2">
         <v>26</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="40" s="1" customFormat="1" spans="1:8">
       <c r="A40" s="2">
         <v>27</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="41" s="1" customFormat="1" spans="1:8">
       <c r="A41" s="2">
         <v>28</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="42" s="1" customFormat="1" spans="1:8">
       <c r="A42" s="2">
         <v>29</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="43" s="1" customFormat="1" spans="1:8">
       <c r="A43" s="2">
         <v>30</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="44" s="1" customFormat="1" spans="1:8">
       <c r="A44" s="2">
         <v>31</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="45" s="1" customFormat="1" spans="1:8">
       <c r="A45" s="2">
         <v>32</v>
       </c>
@@ -8602,18 +8602,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1296296296296" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6296296296296" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6272727272727" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" s="1" customFormat="1" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" s="1" customFormat="1" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -8772,7 +8772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" s="1" customFormat="1" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" s="1" customFormat="1" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="9" s="1" customFormat="1" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="10" s="1" customFormat="1" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="11" s="1" customFormat="1" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="12" s="1" customFormat="1" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="13" s="1" customFormat="1" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="14" s="1" customFormat="1" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="16" s="1" customFormat="1" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="17" s="1" customFormat="1" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="18" s="1" customFormat="1" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="19" s="1" customFormat="1" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="20" s="1" customFormat="1" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -9157,7 +9157,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="21" s="1" customFormat="1" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="26" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A26" s="2">
         <v>13</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="27" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A27" s="2">
         <v>14</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A28" s="2">
         <v>15</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="29" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A29" s="2">
         <v>16</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="30" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A30" s="2">
         <v>17</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="31" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A31" s="2">
         <v>18</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="32" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A32" s="2">
         <v>19</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="33" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A33" s="2">
         <v>20</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="34" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A34" s="2">
         <v>21</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="35" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A35" s="2">
         <v>22</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="36" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A36" s="2">
         <v>23</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="37" s="1" customFormat="1" ht="28" spans="1:9">
       <c r="A37" s="2">
         <v>24</v>
       </c>
@@ -9844,18 +9844,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9959,18 +9959,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10040,18 +10040,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10099,18 +10099,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10214,15 +10214,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="49.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49.7545454545455" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10259,7 +10259,7 @@
       <c r="C2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>271</v>
       </c>
       <c r="E2" s="1">
@@ -10282,7 +10282,7 @@
       <c r="C3" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="1">
@@ -10305,8 +10305,8 @@
       <c r="C4" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>274</v>
+      <c r="D4" t="s">
+        <v>250</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -10318,7 +10318,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -10328,8 +10328,8 @@
       <c r="C5" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>275</v>
+      <c r="D5" t="s">
+        <v>274</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10352,7 +10352,7 @@
         <v>270</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -10391,7 +10391,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -10416,7 +10416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -10445,18 +10445,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10522,16 +10522,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.6272727272727" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.5555555555556" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5545454545455" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10622,7 +10622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -10883,7 +10883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:9">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -11049,7 +11049,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="22" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="23" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="24" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="26" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="72" spans="1:9">
+    <row r="27" s="1" customFormat="1" ht="70" spans="1:9">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -11460,15 +11460,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5545454545455" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11550,7 +11550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A8" s="2">
         <v>13</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A9" s="2">
         <v>14</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A10" s="2">
         <v>15</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A11" s="2">
         <v>16</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A12" s="2">
         <v>17</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A13" s="2">
         <v>18</v>
       </c>
@@ -11964,15 +11964,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5545454545455" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12054,7 +12054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12106,7 +12106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -12210,7 +12210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -12288,7 +12288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -12780,15 +12780,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5545454545455" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12870,7 +12870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13026,7 +13026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -13286,7 +13286,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -13390,7 +13390,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="28.8" spans="1:8">
+    <row r="32" ht="28" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="28.8" spans="1:8">
+    <row r="33" ht="28" spans="1:8">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" ht="28.8" spans="1:8">
+    <row r="34" ht="28" spans="1:8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:8">
+    <row r="35" ht="28" spans="1:8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" ht="28.8" spans="1:8">
+    <row r="36" ht="28" spans="1:8">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" ht="28.8" spans="1:8">
+    <row r="37" ht="28" spans="1:8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" ht="28.8" spans="1:8">
+    <row r="38" ht="28" spans="1:8">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" ht="28.8" spans="1:8">
+    <row r="39" ht="28" spans="1:8">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" ht="28.8" spans="1:8">
+    <row r="40" ht="28" spans="1:8">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" ht="28.8" spans="1:8">
+    <row r="41" ht="28" spans="1:8">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" ht="28.8" spans="1:8">
+    <row r="42" ht="28" spans="1:8">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" ht="28.8" spans="1:8">
+    <row r="43" ht="28" spans="1:8">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -13872,15 +13872,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5545454545455" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -13962,7 +13962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -14352,7 +14352,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="70" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -14606,7 +14606,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -14654,7 +14654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -14678,7 +14678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="28.8" spans="1:8">
+    <row r="32" ht="28" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="28.8" spans="1:8">
+    <row r="33" ht="28" spans="1:8">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -14724,7 +14724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" ht="28.8" spans="1:8">
+    <row r="34" ht="28" spans="1:8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -14747,7 +14747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:8">
+    <row r="35" ht="28" spans="1:8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -14780,14 +14780,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14895,14 +14895,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15105,14 +15105,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15220,14 +15220,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15430,7 +15430,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -15455,7 +15455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -15483,14 +15483,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15554,7 +15554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -15594,7 +15594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:6">
+    <row r="6" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:6">
+    <row r="8" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:6">
+    <row r="9" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:6">
+    <row r="10" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -15698,14 +15698,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15778,7 +15778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -15893,7 +15893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -16008,7 +16008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="16" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -16074,7 +16074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="17" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:7">
+    <row r="18" ht="28" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -16114,7 +16114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:7">
+    <row r="19" ht="28" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:7">
+    <row r="20" ht="28" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -16154,7 +16154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:7">
+    <row r="21" ht="28" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -16174,7 +16174,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:7">
+    <row r="22" ht="28" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" ht="28.8" spans="1:7">
+    <row r="23" ht="28" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -16214,7 +16214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="28.8" spans="1:7">
+    <row r="24" ht="28" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -16244,14 +16244,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16315,7 +16315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -16459,14 +16459,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16539,7 +16539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -16723,7 +16723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="16" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -16835,7 +16835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="17" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="18" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="19" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="20" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -16915,7 +16915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="21" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -16935,7 +16935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="22" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -16955,7 +16955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="23" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="28.8" spans="1:7">
+    <row r="24" ht="28" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -17005,13 +17005,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17061,14 +17061,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17132,7 +17132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -17152,7 +17152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -17212,7 +17212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="10" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -17276,14 +17276,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17676,13 +17676,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17732,7 +17732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:7">
+    <row r="3" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -17755,7 +17755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -17778,7 +17778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -17824,7 +17824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:7">
+    <row r="7" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:7">
+    <row r="8" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:7">
+    <row r="9" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -17893,7 +17893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:7">
+    <row r="10" ht="28" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -17916,7 +17916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:7">
+    <row r="11" ht="28" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:7">
+    <row r="12" ht="28" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -17962,7 +17962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:7">
+    <row r="13" ht="28" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:7">
+    <row r="14" ht="28" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:7">
+    <row r="15" ht="28" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -18031,7 +18031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:7">
+    <row r="16" ht="28" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -18054,7 +18054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:7">
+    <row r="17" ht="28" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -18077,7 +18077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:7">
+    <row r="18" ht="28" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:7">
+    <row r="19" ht="28" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:7">
+    <row r="20" ht="28" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -18146,7 +18146,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:7">
+    <row r="21" ht="28" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -18169,7 +18169,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:7">
+    <row r="22" ht="28" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" ht="28.8" spans="1:7">
+    <row r="23" ht="28" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -18215,7 +18215,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" ht="28.8" spans="1:7">
+    <row r="24" ht="28" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" ht="28.8" spans="1:7">
+    <row r="25" ht="28" spans="1:7">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" ht="28.8" spans="1:7">
+    <row r="26" ht="28" spans="1:7">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -18284,7 +18284,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" ht="28.8" spans="1:7">
+    <row r="27" ht="28" spans="1:7">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -18307,7 +18307,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" ht="28.8" spans="1:7">
+    <row r="28" ht="28" spans="1:7">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" ht="28.8" spans="1:7">
+    <row r="29" ht="28" spans="1:7">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" ht="28.8" spans="1:7">
+    <row r="30" ht="28" spans="1:7">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -18376,7 +18376,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" ht="28.8" spans="1:7">
+    <row r="31" ht="28" spans="1:7">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" ht="28.8" spans="1:7">
+    <row r="32" ht="28" spans="1:7">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" ht="28.8" spans="1:7">
+    <row r="33" ht="28" spans="1:7">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -18535,13 +18535,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18589,14 +18589,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="36.7777777777778" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.7818181818182" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18638,7 +18638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -18668,7 +18668,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -18693,7 +18693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -18721,14 +18721,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.4454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18770,7 +18770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -18800,14 +18800,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18859,12 +18859,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -19533,13 +19533,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -19589,7 +19589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -19612,7 +19612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -19658,7 +19658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>25</v>
       </c>
@@ -19678,7 +19678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>26</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>27</v>
       </c>
@@ -19718,7 +19718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>28</v>
       </c>
@@ -19748,12 +19748,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -19861,13 +19861,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20042,12 +20042,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20355,14 +20355,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20414,13 +20414,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20474,14 +20474,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20533,17 +20533,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20603,7 +20603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -20621,7 +20621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -20649,13 +20649,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20763,14 +20763,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20822,13 +20822,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -20998,14 +20998,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21057,13 +21057,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21173,14 +21173,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21232,14 +21232,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21291,13 +21291,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21407,14 +21407,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21505,14 +21505,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21572,17 +21572,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -21632,14 +21632,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21683,7 +21683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -21703,7 +21703,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -21723,7 +21723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -21743,7 +21743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -21760,7 +21760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -21792,14 +21792,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -21826,7 +21826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -21893,7 +21893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -21916,7 +21916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -21959,7 +21959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -21979,7 +21979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:7">
+    <row r="9" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -22015,14 +22015,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7818181818182" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22063,7 +22063,7 @@
         <v>582</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>583</v>
@@ -22072,7 +22072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -22086,14 +22086,14 @@
         <v>585</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -22107,7 +22107,7 @@
         <v>587</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>588</v>
@@ -22126,13 +22126,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22197,13 +22197,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22285,13 +22285,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22356,13 +22356,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22410,13 +22410,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22464,13 +22464,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22534,7 +22534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -22564,13 +22564,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.5555555555556" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.5545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5545454545455" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -22620,7 +22620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -22643,7 +22643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -22666,7 +22666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="28" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:7">
+    <row r="7" ht="28" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -22735,7 +22735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:7">
+    <row r="8" ht="28" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -22755,7 +22755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:7">
+    <row r="9" ht="28" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -22775,7 +22775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:7">
+    <row r="10" ht="28" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -22795,7 +22795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:7">
+    <row r="11" ht="28" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -22825,17 +22825,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:6">
+    <row r="10" ht="28" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -23032,7 +23032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:6">
+    <row r="11" ht="28" spans="1:6">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -23059,13 +23059,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23113,13 +23113,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.5555555555556" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.5545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
     <col min="4" max="7" width="28.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23457,13 +23457,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23511,15 +23511,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="5" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.6666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.6636363636364" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23575,7 +23575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -23608,13 +23608,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="7" width="20.4444444444444" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="7" width="20.4454545454545" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23670,7 +23670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:8">
+    <row r="3" ht="28" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -23696,7 +23696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:8">
+    <row r="4" ht="28" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -23755,13 +23755,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="5" width="34.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6636363636364" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23805,7 +23805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -23825,7 +23825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -23852,13 +23852,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="5" width="34.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6636363636364" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -23902,7 +23902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -23922,7 +23922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -23950,13 +23950,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -24004,13 +24004,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="5" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -24118,13 +24118,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6636363636364" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -24172,17 +24172,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5545454545455" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
